--- a/backend/templates/pr-template.xlsx
+++ b/backend/templates/pr-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\web-opr\backend\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090DD502-CD9A-410F-9060-919E15C94D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9806470-53DE-4F87-9B25-A0BDCC2ADC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PR page 1" sheetId="126" r:id="rId1"/>
@@ -506,6 +506,68 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
@@ -527,12 +589,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -571,62 +627,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1040,6 +1040,7 @@
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="6" width="13.54296875" customWidth="1"/>
     <col min="7" max="7" width="8.7265625" customWidth="1"/>
+    <col min="12" max="12" width="35.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1047,26 +1048,26 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="68"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="54"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="71"/>
+      <c r="A2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="72"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="74"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="60"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1074,63 +1075,63 @@
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="27"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="76"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="62"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="78"/>
+      <c r="B5" s="64"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="80"/>
+      <c r="F5" s="66"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="81"/>
-      <c r="B6" s="82"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="48"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="85" t="s">
+      <c r="E6" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="86"/>
+      <c r="F6" s="46"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="E7" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="52" t="s">
+      <c r="F7" s="51" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="84"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
+      <c r="A8" s="50"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
     </row>
     <row r="9" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8"/>
@@ -1139,7 +1140,7 @@
       <c r="D9" s="29"/>
       <c r="E9" s="42"/>
       <c r="F9" s="39">
-        <f>D9*E9</f>
+        <f t="shared" ref="F9:F34" si="0">D9*E9</f>
         <v>0</v>
       </c>
     </row>
@@ -1150,7 +1151,7 @@
       <c r="D10" s="23"/>
       <c r="E10" s="43"/>
       <c r="F10" s="39">
-        <f>D10*E10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1161,7 +1162,7 @@
       <c r="D11" s="30"/>
       <c r="E11" s="43"/>
       <c r="F11" s="39">
-        <f>D11*E11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1172,7 +1173,7 @@
       <c r="D12" s="30"/>
       <c r="E12" s="43"/>
       <c r="F12" s="39">
-        <f>D12*E12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1183,7 +1184,7 @@
       <c r="D13" s="30"/>
       <c r="E13" s="43"/>
       <c r="F13" s="39">
-        <f>D13*E13</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1194,7 +1195,7 @@
       <c r="D14" s="30"/>
       <c r="E14" s="43"/>
       <c r="F14" s="39">
-        <f>D14*E14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1205,7 +1206,7 @@
       <c r="D15" s="30"/>
       <c r="E15" s="43"/>
       <c r="F15" s="39">
-        <f>D15*E15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1216,7 +1217,7 @@
       <c r="D16" s="30"/>
       <c r="E16" s="43"/>
       <c r="F16" s="39">
-        <f>D16*E16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1227,7 +1228,7 @@
       <c r="D17" s="30"/>
       <c r="E17" s="43"/>
       <c r="F17" s="39">
-        <f>D17*E17</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1238,7 +1239,7 @@
       <c r="D18" s="30"/>
       <c r="E18" s="43"/>
       <c r="F18" s="39">
-        <f>D18*E18</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1249,7 +1250,7 @@
       <c r="D19" s="30"/>
       <c r="E19" s="40"/>
       <c r="F19" s="39">
-        <f>D19*E19</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1260,7 +1261,7 @@
       <c r="D20" s="32"/>
       <c r="E20" s="44"/>
       <c r="F20" s="39">
-        <f>D20*E20</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1271,7 +1272,7 @@
       <c r="D21" s="32"/>
       <c r="E21" s="44"/>
       <c r="F21" s="39">
-        <f>D21*E21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1282,7 +1283,7 @@
       <c r="D22" s="30"/>
       <c r="E22" s="41"/>
       <c r="F22" s="39">
-        <f>D22*E22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1293,7 +1294,7 @@
       <c r="D23" s="30"/>
       <c r="E23" s="40"/>
       <c r="F23" s="39">
-        <f>D23*E23</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1304,7 +1305,7 @@
       <c r="D24" s="30"/>
       <c r="E24" s="40"/>
       <c r="F24" s="39">
-        <f>D24*E24</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1315,7 +1316,7 @@
       <c r="D25" s="30"/>
       <c r="E25" s="40"/>
       <c r="F25" s="39">
-        <f>D25*E25</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1326,7 +1327,7 @@
       <c r="D26" s="30"/>
       <c r="E26" s="40"/>
       <c r="F26" s="39">
-        <f>D26*E26</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1337,7 +1338,7 @@
       <c r="D27" s="30"/>
       <c r="E27" s="40"/>
       <c r="F27" s="39">
-        <f>D27*E27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1348,7 +1349,7 @@
       <c r="D28" s="30"/>
       <c r="E28" s="40"/>
       <c r="F28" s="39">
-        <f>D28*E28</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1359,7 +1360,7 @@
       <c r="D29" s="30"/>
       <c r="E29" s="40"/>
       <c r="F29" s="39">
-        <f>D29*E29</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1370,7 +1371,7 @@
       <c r="D30" s="30"/>
       <c r="E30" s="40"/>
       <c r="F30" s="39">
-        <f>D30*E30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1381,7 +1382,7 @@
       <c r="D31" s="30"/>
       <c r="E31" s="40"/>
       <c r="F31" s="39">
-        <f>D31*E31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1392,7 +1393,7 @@
       <c r="D32" s="30"/>
       <c r="E32" s="40"/>
       <c r="F32" s="39">
-        <f>D32*E32</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1403,7 +1404,7 @@
       <c r="D33" s="30"/>
       <c r="E33" s="40"/>
       <c r="F33" s="39">
-        <f>D33*E33</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1414,7 +1415,7 @@
       <c r="D34" s="38"/>
       <c r="E34" s="40"/>
       <c r="F34" s="39">
-        <f>D34*E34</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1422,44 +1423,44 @@
       <c r="A35" s="12"/>
       <c r="B35" s="13"/>
       <c r="C35" s="14"/>
-      <c r="D35" s="54" t="s">
+      <c r="D35" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="55"/>
+      <c r="E35" s="75"/>
       <c r="F35" s="9">
         <f>SUM(F9:F34)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="64" t="s">
+      <c r="A36" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="B36" s="65"/>
-      <c r="C36" s="65"/>
-      <c r="D36" s="65"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="66"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="85"/>
+      <c r="D36" s="85"/>
+      <c r="E36" s="85"/>
+      <c r="F36" s="86"/>
     </row>
     <row r="37" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="56"/>
-      <c r="B37" s="57"/>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="58"/>
+      <c r="A37" s="76"/>
+      <c r="B37" s="77"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="78"/>
     </row>
     <row r="38" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="59" t="s">
+      <c r="A38" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="60"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="62" t="s">
+      <c r="B38" s="80"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="62"/>
-      <c r="F38" s="63"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="83"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
@@ -1467,9 +1468,9 @@
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="21"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="47"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="69"/>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
@@ -1477,9 +1478,9 @@
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="16"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="49"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="71"/>
     </row>
     <row r="41" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="17" t="s">
@@ -1487,11 +1488,11 @@
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="22"/>
-      <c r="D41" s="50" t="s">
+      <c r="D41" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="E41" s="50"/>
-      <c r="F41" s="51"/>
+      <c r="E41" s="72"/>
+      <c r="F41" s="73"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="6"/>
@@ -1506,18 +1507,6 @@
     <sortCondition ref="K6:K22"/>
   </sortState>
   <mergeCells count="23">
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:F5"/>
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
@@ -1529,6 +1518,18 @@
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="C36:F36"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="97" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/backend/templates/pr-template.xlsx
+++ b/backend/templates/pr-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9806470-53DE-4F87-9B25-A0BDCC2ADC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE591751-E1A1-493C-A7FB-FF6C53F9F81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -116,7 +116,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,11 +183,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -384,9 +379,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -407,11 +402,8 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -442,13 +434,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -463,31 +455,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -500,12 +489,116 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -523,110 +616,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1031,7 +1020,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.54296875" customWidth="1"/>
@@ -1048,491 +1037,425 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="54"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="66"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
+      <c r="A2" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="69"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="58"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="60"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="72"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="62"/>
-    </row>
-    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="63" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="74"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="64"/>
+      <c r="B5" s="76"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="65" t="s">
+      <c r="E5" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="66"/>
+      <c r="F5" s="78"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="47"/>
-      <c r="B6" s="48"/>
+      <c r="A6" s="81"/>
+      <c r="B6" s="82"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="46"/>
+      <c r="F6" s="80"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="50" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="50"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-    </row>
-    <row r="9" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="84"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="8"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="39">
-        <f t="shared" ref="F9:F34" si="0">D9*E9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="27"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="37">
+        <f t="shared" ref="F9:F28" si="0">D9*E9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="8"/>
-      <c r="B10" s="23"/>
+      <c r="B10" s="22"/>
       <c r="C10" s="10"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D10" s="22"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="8"/>
-      <c r="B11" s="23"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D11" s="29"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
-      <c r="B12" s="23"/>
+      <c r="B12" s="22"/>
       <c r="C12" s="10"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D12" s="29"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="8"/>
-      <c r="B13" s="23"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="10"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D13" s="29"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="8"/>
-      <c r="B14" s="23"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="10"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D14" s="29"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="8"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="22"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="23"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="10"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D16" s="29"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="8"/>
-      <c r="B17" s="23"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D17" s="29"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
-      <c r="B18" s="23"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D18" s="29"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
-      <c r="B19" s="23"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D19" s="29"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="8"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="31"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="8"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="31"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="8"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="32"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="8"/>
-      <c r="B23" s="25"/>
+      <c r="B23" s="24"/>
       <c r="C23" s="10"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D23" s="29"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="8"/>
-      <c r="B24" s="25"/>
+      <c r="B24" s="24"/>
       <c r="C24" s="10"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D24" s="29"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="8"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="24"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="8"/>
-      <c r="B26" s="25"/>
+      <c r="B26" s="24"/>
       <c r="C26" s="10"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D26" s="29"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="8"/>
-      <c r="B27" s="24"/>
+      <c r="B27" s="23"/>
       <c r="C27" s="10"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D27" s="29"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="8"/>
-      <c r="B28" s="24"/>
+      <c r="B28" s="23"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="39">
+      <c r="D28" s="29"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="8"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="8"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="8"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="8"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="8"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="12"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="74" t="s">
+      <c r="A29" s="11"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="75"/>
-      <c r="F35" s="9">
-        <f>SUM(F9:F34)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="84" t="s">
+      <c r="E29" s="53"/>
+      <c r="F29" s="9">
+        <f>SUM(F9:F28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="B36" s="85"/>
-      <c r="C36" s="85"/>
-      <c r="D36" s="85"/>
-      <c r="E36" s="85"/>
-      <c r="F36" s="86"/>
-    </row>
-    <row r="37" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="76"/>
-      <c r="B37" s="77"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="78"/>
-    </row>
-    <row r="38" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="79" t="s">
+      <c r="B30" s="63"/>
+      <c r="C30" s="63"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="64"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="54"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="56"/>
+    </row>
+    <row r="32" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="80"/>
-      <c r="C38" s="81"/>
-      <c r="D38" s="82" t="s">
+      <c r="B32" s="58"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="82"/>
-      <c r="F38" s="83"/>
-    </row>
-    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
+      <c r="E32" s="60"/>
+      <c r="F32" s="61"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="69"/>
-    </row>
-    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
+      <c r="B33" s="14"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="45"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="71"/>
-    </row>
-    <row r="41" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="17" t="s">
+      <c r="B34" s="14"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="47"/>
+    </row>
+    <row r="35" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="72" t="s">
+      <c r="B35" s="17"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E41" s="72"/>
-      <c r="F41" s="73"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="6"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="20"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="49"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="6"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="19"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K6:K22">
     <sortCondition ref="K6:K22"/>
   </sortState>
   <mergeCells count="23">
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:F30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="97" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="97" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/backend/templates/pr-template.xlsx
+++ b/backend/templates/pr-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE591751-E1A1-493C-A7FB-FF6C53F9F81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9AA745-C851-4A0C-9459-686908A99D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -495,6 +495,68 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
@@ -516,12 +578,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -560,62 +616,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1020,7 +1020,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.54296875" customWidth="1"/>
@@ -1037,26 +1037,26 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="52"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="69"/>
+      <c r="A2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="55"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="72"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="58"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1064,63 +1064,63 @@
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="26"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="74"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="60"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="76"/>
+      <c r="B5" s="62"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="77" t="s">
+      <c r="E5" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="78"/>
+      <c r="F5" s="64"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="81"/>
-      <c r="B6" s="82"/>
+      <c r="A6" s="45"/>
+      <c r="B6" s="46"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="79" t="s">
+      <c r="E6" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="80"/>
+      <c r="F6" s="44"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="50" t="s">
+      <c r="D7" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="49" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="84"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
+      <c r="A8" s="48"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
     </row>
     <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="8"/>
@@ -1129,7 +1129,7 @@
       <c r="D9" s="28"/>
       <c r="E9" s="40"/>
       <c r="F9" s="37">
-        <f t="shared" ref="F9:F28" si="0">D9*E9</f>
+        <f t="shared" ref="F9:F33" si="0">D9*E9</f>
         <v>0</v>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
     <row r="25" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="8"/>
       <c r="B25" s="24"/>
-      <c r="C25" s="36"/>
+      <c r="C25" s="10"/>
       <c r="D25" s="29"/>
       <c r="E25" s="38"/>
       <c r="F25" s="37">
@@ -1322,7 +1322,7 @@
     </row>
     <row r="27" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="8"/>
-      <c r="B27" s="23"/>
+      <c r="B27" s="24"/>
       <c r="C27" s="10"/>
       <c r="D27" s="29"/>
       <c r="E27" s="38"/>
@@ -1333,7 +1333,7 @@
     </row>
     <row r="28" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="8"/>
-      <c r="B28" s="23"/>
+      <c r="B28" s="24"/>
       <c r="C28" s="10"/>
       <c r="D28" s="29"/>
       <c r="E28" s="38"/>
@@ -1342,117 +1342,172 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="11"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="52" t="s">
+    <row r="29" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="8"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="8"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="8"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="8"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="8"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="11"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="53"/>
-      <c r="F29" s="9">
-        <f>SUM(F9:F28)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="62" t="s">
+      <c r="E34" s="73"/>
+      <c r="F34" s="9">
+        <f>SUM(F9:F33)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="B30" s="63"/>
-      <c r="C30" s="63"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="63"/>
-      <c r="F30" s="64"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="54"/>
-      <c r="B31" s="55"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="56"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="57" t="s">
+      <c r="B35" s="83"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="84"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="74"/>
+      <c r="B36" s="75"/>
+      <c r="C36" s="75"/>
+      <c r="D36" s="75"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="76"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="B32" s="58"/>
-      <c r="C32" s="59"/>
-      <c r="D32" s="60" t="s">
+      <c r="B37" s="78"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="60"/>
-      <c r="F32" s="61"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
+      <c r="E37" s="80"/>
+      <c r="F37" s="81"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="45"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
+      <c r="B38" s="14"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="67"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="47"/>
-    </row>
-    <row r="35" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="16" t="s">
+      <c r="B39" s="14"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="69"/>
+    </row>
+    <row r="40" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="48" t="s">
+      <c r="B40" s="17"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="48"/>
-      <c r="F35" s="49"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="6"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="19"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="71"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="6"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="19"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K6:K22">
     <sortCondition ref="K6:K22"/>
   </sortState>
   <mergeCells count="23">
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:F30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="97" orientation="portrait" r:id="rId1"/>
